--- a/Result/checksun_type/零組件_材料.xlsx
+++ b/Result/checksun_type/零組件_材料.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>98.74000000000001</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>108.4</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>114.86</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>114.86</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>225633569.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>250132082.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>250132082.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>342636057.8</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>396887465.98</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>396887465.98</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-66057250.03203994</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>225633569</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>225633569.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>97.64000000000001</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>109.54</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>115.15</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>109.54</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>115.15</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>188954117.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>307098882.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>307098882.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>371905664.8</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>399902695.5</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>399902695.5</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-62936675.5043838</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>188954117</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>188954117.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>97.38</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>110.74</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>115.54</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>110.74</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>115.54</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>336078160.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>373422126.2</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>373422126.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>409366105.1</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>402312395.44</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>402312395.44</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-52301032.19686127</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>336078160</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>336078160.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>98.08</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>112.0</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>115.98</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>112</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>115.98</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>234306761.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>359114982.6</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>359114982.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>469727069.9</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>407067817.72</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>407067817.72</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-51002652.35765541</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>234306761</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>234306761.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>98.88</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>113.27</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>116.48</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>113.27</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>116.48</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>265687805.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>395419078.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>395419078</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>559586505.7</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>407163058.94</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>407163058.94</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-36422222.25315934</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>265687805</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>265687805.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>99.84</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>114.48</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>116.95</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>114.48</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>116.95</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>510467568.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>435140033.2</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>435140033.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>733288345.2</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>405490068.5</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>405490068.5</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-17654497.45198071</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>510467568</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>510467568.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>101.34</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>115.81</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>117.49</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>115.81</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>117.49</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>520570337.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>436712447.4</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>436712447.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>726492067.5</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>399448998.5</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>399448998.5</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-16439347.43415487</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>520570337</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>520570337.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>102.3</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>116.72</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>117.99</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>116.72</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>117.99</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>264542442.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>445310084.0</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>445310084</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>714346987.1</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>391687635.72</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>391687635.72</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-15198738.82175517</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>264542442</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>264542442.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>103.2</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>117.62</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>118.42</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>117.62</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>118.42</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>415827238.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>580339157.2</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>580339157.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>773267969.9</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>390545731.7</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>390545731.7</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>14547931.47530699</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>415827238</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>415827238.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>105.2</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>118.58</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>118.83</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>118.58</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>118.83</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>464292581.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>723753933.4</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>723753933.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>773455271.2</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>389650213.94</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>389650213.94</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>40314520.48984909</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>464292581</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>464292581.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>108.1</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>119.3</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>119.31</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>119.3</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>119.31</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>518329639.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>1031436657.2</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>1031436657.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>800761249.4</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>386253013.42</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>386253013.42</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>70491413.7431289</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>518329639</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>518329639.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>121.5</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>123.98</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>119.29</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>123.98</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>119.29</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>116792257.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>156567321.4</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>156567321.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>189454064.4</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>318150407.34</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>318150407.34</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-35640807.2288911</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>116792257</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>116792257.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>121.3</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>123.78</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>119.06</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>123.78</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>119.06</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>143570356.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>190225454.4</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>190225454.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>215742345.5</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>318733821.76</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>318733821.76</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-33370636.02417654</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>143570356</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>143570356.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>120.8</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>123.58</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>118.88</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>123.58</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>118.88</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>136096754.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>206130143.4</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>206130143.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>221377285.3</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>318478020.68</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>318478020.68</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-31804807.90943512</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>136096754</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>136096754.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>121.3</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>123.58</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>118.73</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>123.58</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>118.73</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>166072395.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>203391625.4</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>203391625.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>240690842.7</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>318219735.08</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>318219735.08</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-27631281.53446758</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>166072395</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>166072395.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>122.3</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>123.58</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>118.63</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>123.58</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>118.63</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>220304845.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>213645726.0</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>213645726</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>249224824.6</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>318339495.48</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>318339495.48</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-23893945.33685437</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>220304845</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>220304845.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>123.6</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>123.42</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>118.47</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>123.42</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>118.47</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>285082922.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>222340807.4</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>222340807.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>250119491.9</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>316878790.8</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>316878790.8</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-23512158.07823354</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>285082922</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>285082922.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>124.6</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>123.1</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>118.31</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>123.1</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>118.31</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>223093801.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>241259236.6</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>241259236.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>251423710.6</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>315242401.56</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>315242401.56</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-29067536.02740973</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>223093801</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>223093801.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>125.6</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>122.78</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>118.16</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>122.78</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>118.16</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>122404164.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>236624427.2</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>236624427.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>278228999.2</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>313300516.2</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>313300516.2</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-29323972.41811109</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>122404164</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>122404164.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>126.0</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>122.28</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>117.91</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>122.28</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>117.91</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>217342898.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>277990060.0</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>277990060</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>338438970.1</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>312973362.38</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>312973362.38</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-17854849.99703753</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>217342898</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>217342898.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>125.4</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>121.6</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>117.66</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>121.6</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>117.66</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>263780252.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>284803923.2</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>284803923.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>409270685.2</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>312412010.72</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>312412010.72</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-11004723.39560974</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>263780252</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>263780252.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>125.2</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>120.62</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>117.36</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>120.62</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>117.36</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>379675068.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>277898176.4</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>277898176.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>437448534.2</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>311595701.46</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>311595701.46</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-5801233.20086962</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>379675068</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>379675068.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>40.72</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>43.4</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>48.55</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>48.55</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>35672.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>28487.0</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>28487</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>34170.1</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>41437.42</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>41437.42</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-4188.239231822641</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>35672</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>35672.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>40.2</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>43.84</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>48.81</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>43.84</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>48.81</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>22526.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>28958.8</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>28958.8</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>41710.4</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>41791.56</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>41791.56</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-4926.580826009347</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>22526</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>22526.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>40.13</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>44.28</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>49.14</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>49.14</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>21891.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>31912.6</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>31912.6</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>42976.3</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>42219.3</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>42219.3</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-4396.905216775725</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>21891</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>21891.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>40.39</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>44.72</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>49.49</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>44.72</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>49.49</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>29401.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>35745.4</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>35745.4</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>45604.3</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>42494.14</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>42494.14</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-3415.157731557134</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>29401</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>29401.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>41.22000000000001</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>45.22</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>49.87</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>45.22</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>49.87</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>32945.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>35478.0</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>35478</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>47085.3</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>42451.16</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>42451.16</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-2695.33426226068</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>32945</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>32945.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>42.0</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>45.75</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>50.22</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>45.75</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>50.22</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>38031.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>39853.2</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>39853.2</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>48084.7</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>42275.62</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>42275.62</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-1950.467368185011</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>38031</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>38031.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>43.26000000000001</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>46.31</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>50.6</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>46.31</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>50.6</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>37295.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>54462.0</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>54462</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>48707.4</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>42048.32</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>42048.32</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-1361.640827784584</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>37295</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>37295.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>43.86</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>46.83</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>50.98</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>46.83</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>50.98</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>41055.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>54040.0</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>54040</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>50782.7</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>41867.08</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>41867.08</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-392.9728833631088</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>41055</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>41055.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>44.1</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>47.23</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>51.32</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>47.23</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>51.32</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>28064.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>55463.2</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>55463.2</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>55843.3</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>42118.1</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>42118.1</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>602.0160687876851</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>28064</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>28064.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>44.02</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>47.57</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>51.65</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>47.57</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>51.65</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>54821.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>58692.6</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>58692.6</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>56745.3</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>43111.12</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>43111.12</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>3393.821140832108</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>54821</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>54821.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>43.98</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>47.77</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>52.0</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>47.77</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>52</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>111075.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>56316.2</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>56316.2</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>59575.9</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>43603.2</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>43603.2</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>4394.084774437288</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>111075</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>111075.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>469.8</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>447.05</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>446.77</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>447.05</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>446.77</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>1423632.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>1074436.2</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>1074436.2</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>1110590.0</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>889509.16</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>889509.16</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>66304.72144113004</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>1423632</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>1423632.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>460.3</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>443.95</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>445.52</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>443.95</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>445.52</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>1425639.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>952434.4</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>952434.4</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>1232385.1</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>897175.66</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>897175.66</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>42160.62828500872</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>1425639</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>1425639.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>454.3</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>441.8</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>444.92</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>441.8</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>444.92</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>1193287.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>799270.2</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>799270.2</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>1162535.1</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>905113.32</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>905113.3199999999</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>5948.294194656424</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>1193287</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>1193287.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>450.7</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>440.5</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>444.09</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>440.5</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>444.09</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>608812.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>681135.0</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>681135</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>1076795.9</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>946635.86</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>946635.86</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-21101.19358422747</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>608812</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>608812.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>453.9</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>440.32</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>443.76</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>440.32</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>443.76</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>720811.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>737167.0</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>737167</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>1051519.2</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>946400.84</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>946400.84</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>3632.616502517951</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>720811</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>720811.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>455.2</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>440.18</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>443.28</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>440.18</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>443.28</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>813623.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>1146743.8</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>1146743.8</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>1036060.4</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>951886.0</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>951886</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>26837.00175135012</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>813623</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>813623.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>459.3</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>441.28</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>443.04</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>441.28</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>443.04</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>659818.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>1512335.8</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>1512335.8</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>994681.9</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>979869.06</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>979869.0600000001</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>49083.51632999082</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>659818</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>659818.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>454.4</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>441.98</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>442.88</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>441.98</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>442.88</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>602611.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>1525800.0</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>1525800</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>968929.7</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>1047671.32</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>1047671.32</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>95590.37585912063</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>602611</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>602611.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>449.4</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>441.4</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>441.76</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>441.4</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>441.76</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>888972.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>1472456.8</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>1472456.8</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>971366.9</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>1067969.98</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>1067969.98</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>164744.1260486231</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>888972</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>888972.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>442.6</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>440.9</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>440.2</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>440.9</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>440.2</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>2768695.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>1365871.4</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>1365871.4</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>1001566.6</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>1079083.12</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>1079083.12</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>226969.943246176</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>2768695</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>2768695.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>436.1</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>439.22</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>438.77</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>439.22</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>438.77</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>2641583.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>925377.0</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>925377</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>794799.3</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>1044638.5</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>1044638.5</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>106359.0055553169</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>2641583</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>2641583.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>28.62</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>30.42</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>29.92</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>30.42</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>55456257.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>58015182.4</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>58015182.4</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>52827359.3</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>123115763.48</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>123115763.48</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-10378487.87877303</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>55456257</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>55456257.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>28.36</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>30.12</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>30.39</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>30.12</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>30.39</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>81199919.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>55383180.8</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>55383180.8</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>53268551.0</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>123799309.52</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>123799309.52</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-11134529.26355028</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>81199919</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>81199919.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>28.35</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>30.33</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>30.39</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>30.33</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>30.39</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>94716573.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>49136500.6</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>49136500.6</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>48785764.2</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>123544518.18</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>123544518.18</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-14575176.12524812</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>94716573</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>94716573.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>30.5</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>30.39</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>30.39</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>26140369.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>38252971.2</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>38252971.2</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>42975338.2</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>124503121.72</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>124503121.72</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-20418056.85177189</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>26140369</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>26140369.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>28.89</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>30.72</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>30.41</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>30.72</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>30.41</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>32562794.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>41757212.0</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>41757212</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>45577676.6</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>124711001.24</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>124711001.24</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-20688362.57352827</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>32562794</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>32562794.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>29.29</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>30.9</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>30.41</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>30.41</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>42296249.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>47639536.2</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>47639536.2</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>51011940.4</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>125381020.74</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>125381020.74</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-21023760.47698283</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>42296249</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>42296249.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>29.79</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>31.16</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>30.43</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>31.16</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>30.43</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>49966518.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>51153921.2</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>51153921.2</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>63020791.2</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>126597383.28</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>126597383.28</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-21794921.92916852</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>49966518</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>49966518.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>29.96</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>31.36</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>30.43</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>31.36</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>30.43</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>40298926.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>48435027.8</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>48435027.8</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>68001781.7</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>127187028.66</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>127187028.66</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-22940005.61339204</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>40298926</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>40298926.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>29.87</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>31.51</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>30.38</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>31.51</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>30.38</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>43661573.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>47697705.2</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>47697705.2</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>78842006.0</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>126919433.3</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>126919433.3</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-22720740.10466164</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>43661573</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>43661573.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>29.7</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>31.68</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>30.31</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>31.68</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>30.31</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>61974415.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>49398141.2</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>49398141.2</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>97585237.6</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>127112973.48</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>127112973.48</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-21956332.26702316</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>61974415</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>61974415.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>29.53</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>31.8</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>30.28</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>30.28</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>59868174.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>54384344.6</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>54384344.6</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>159704889.2</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>126523628.7</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>126523628.7</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-22042256.56086023</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>59868174</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>59868174.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>203.0</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>217.92</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>229.57</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>217.92</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>229.57</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>246990.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>261303.6</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>261303.6</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>360072.2</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>1087687.9</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>1087687.9</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-60756.27700912725</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>246990</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>246990.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>201.2</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>219.42</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>229.64</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>219.42</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>229.64</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>188584.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>277235.2</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>277235.2</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>364259.9</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>1109012.44</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>1109012.44</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-62901.108610934</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>188584</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>188584.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>200.9</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>221.0</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>229.9</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>221</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>229.9</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>266834.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>327128.4</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>327128.4</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>378625.9</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>1132112.48</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>1132112.48</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-57460.89987741027</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>266834</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>266834.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>203.5</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>223.02</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>230.31</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>223.02</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>230.31</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>328496.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>351582.6</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>351582.6</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>393659.8</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>1170503.62</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>1170503.62</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-56020.92669104022</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>328496</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>328496.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>206.5</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>225.2</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>230.45</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>225.2</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>230.45</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>275614.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>419383.0</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>419383</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>399217.9</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>1181679.14</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>1181679.14</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-58569.71761440305</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>275614</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>275614.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>209.8</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>227.1</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>230.35</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>227.1</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>230.35</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>326648.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>458840.8</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>458840.8</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>399885.8</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>1187183.2</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>1187183.2</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>-54453.1433044069</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>326648</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>326648.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>214.9</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>229.28</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>230.34</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>229.28</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>230.34</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>438050.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>451284.6</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>451284.6</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>403006.7</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>1190565.96</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>1190565.96</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>-52095.49631496938</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>438050</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>438050.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>219.1</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>230.98</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>230.29</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>230.98</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>230.29</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>389105.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>430123.4</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>430123.4</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>398138.1</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>1191948.4</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>1191948.4</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>-58802.80431880965</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>389105</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>389105.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>222.5</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>232.15</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>229.96</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>232.15</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>229.96</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>667498.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>435737.0</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>435737</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>393344.8</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>1189336.42</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>1189336.42</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>-61040.46559862403</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>667498</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>667498.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>225.1</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>233.28</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>229.57</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>233.28</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>229.57</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>472903.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>379052.8</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>379052.8</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>373683.5</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>1181965.28</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>1181965.28</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>-91884.92936983652</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>472903</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>472903.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>226.8</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>233.52</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>229.07</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>233.52</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>229.07</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>288867.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>340930.8</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>340930.8</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>402140.3</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>1178670.4</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>1178670.4</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>-111817.3801369317</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>288867</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>288867.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>47.75</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>51.42</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>55.67</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>51.42</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>55.67</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>2423.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>1862.0</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>1862</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>1805.8</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>3201.88</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>3201.88</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>-117.2067175660754</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>2423</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>2423.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>47.56</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>51.91</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>55.89</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>51.91</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>55.89</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>1310.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>1832.8</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>1832.8</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>1658.7</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>3342.72</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>3342.72</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>-198.5064092676969</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>1310</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>1310.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>47.73999999999999</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>52.46</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>56.18</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>52.46</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>56.18</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>726.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>1817.6</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>1817.6</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>1672.5</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>3467.52</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>3467.52</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>-188.3093113675957</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>726</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>726.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>48.34</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>53.0</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>56.48</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>53</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>56.48</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>3073.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>1987.2</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>1987.2</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>1692.8</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>3584.26</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>3584.26</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>-104.4452675328939</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>3073</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>3073.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>49.05</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>53.56</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>56.81</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>53.56</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>56.81</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>1778.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>1641.2</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>1641.2</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>1490.7</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>3662.0</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>3662</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>-232.3735882142887</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>1778</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>1778.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>49.11</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>53.99</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>57.08</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>53.99</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>57.08</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>2277.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>1749.6</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>1749.6</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>1472.0</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>3865.82</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>3865.82</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>-268.0792753229132</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>2277</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>2277.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>49.94</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>54.55</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>57.38</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>54.55</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>57.38</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>1234.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>1484.6</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>1484.6</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>1474.5</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>4258.62</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>4258.62</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>-362.9774256451299</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>1234</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>1234.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>50.66</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>55.02</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>57.71</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>55.02</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>57.71</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>1574.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>1527.4</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>1527.4</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>1617.2</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>4550.92</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>4550.92</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>-373.832732332399</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>1574</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>1574.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>51.02</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>55.42</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>57.94</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>55.42</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>57.94</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>1343.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>1398.4</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>1398.4</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>1578.0</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>4744.4</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>4744.4</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>-412.4177157309118</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>1343</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>1343.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>51.58</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>55.8</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>58.21</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>58.21</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>2320.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>1340.2</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>1340.2</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>2194.2</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>5094.5</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>5094.5</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>-428.0599164526834</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>2320</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>2320.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>52.38</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>56.05</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>58.48</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>56.05</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>58.48</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>952.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>1194.4</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>1194.4</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>2079.8</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>6976.7</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>6976.7</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>-539.7966347533327</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>952</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>952.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33983,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34167,11 @@
           <t>123.4</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>120.69</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>105.83</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>120.69</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>105.83</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34218,16 @@
           <t>4568862.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>1952768.4</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>1952768.4</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>1481249.8</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>1015366.44</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>1015366.44</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34244,10 @@
           <t>276038.9431784172</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>4568862</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>4568862.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34413,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34597,11 @@
           <t>120.6</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>119.16</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>104.95</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>119.16</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>104.95</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34648,16 @@
           <t>3307114.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>1161408.0</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>1161408</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>1155210.7</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>931524.28</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>931524.28</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34674,10 @@
           <t>40378.12940243562</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>3307114</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>3307114.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34843,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35027,11 @@
           <t>117.7</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>117.46</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>104.08</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>117.46</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>104.08</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35078,16 @@
           <t>373660.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>629111.6</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>629111.6</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>931292.5</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>869506.98</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>869506.98</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35104,10 @@
           <t>-162534.9663276251</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>373660</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>373660.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35273,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35457,11 @@
           <t>117.9</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>116.44</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>103.46</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>116.44</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>103.46</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35508,16 @@
           <t>791273.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>689238.6</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>689238.6</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>991167.9</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>865795.64</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>865795.64</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35534,10 @@
           <t>-132307.3542874394</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>791273</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>791273.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35703,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35887,11 @@
           <t>119.7</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>115.81</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>103.07</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>115.81</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>103.07</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35938,16 @@
           <t>722933.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>798369.0</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>798369</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>1036373.0</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>855958.02</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>855958.02</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35964,10 @@
           <t>-129144.0387197656</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>722933</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>722933.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36133,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36317,11 @@
           <t>121.9</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>114.88</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>102.51</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>114.88</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>102.51</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36368,16 @@
           <t>612060.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>1009731.2</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>1009731.2</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>1224660.7</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>846520.7</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>846520.7</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36394,10 @@
           <t>-112690.5865259543</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>612060</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>612060.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36563,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36747,11 @@
           <t>123.0</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>114.01</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>101.96</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>114.01</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>101.96</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36798,16 @@
           <t>645632.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>1149013.4</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>1149013.4</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>1516328.8</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>839280.96</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>839280.96</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36824,10 @@
           <t>-73281.74101601099</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>645632</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>645632.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36993,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37177,11 @@
           <t>123.5</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>112.81</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>101.38</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>112.81</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>101.38</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37228,16 @@
           <t>674295.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>1233473.4</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>1233473.4</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>1959453.6</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>832026.8</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>832026.8</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37254,10 @@
           <t>-17963.18525123433</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>674295</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>674295.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37423,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37607,11 @@
           <t>123.0</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>111.4</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>100.71</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>111.4</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>100.71</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37658,16 @@
           <t>1336925.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>1293097.2</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>1293097.2</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>2088733.9</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>823424.2</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>823424.2</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37684,10 @@
           <t>58633.82960027573</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>1336925</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>1336925.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37853,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38037,11 @@
           <t>123.1</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>110.23</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>100.13</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>110.23</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>100.13</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38088,16 @@
           <t>1779744.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>1274377.0</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>1274377</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>2215675.5</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>803814.42</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>803814.42</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38114,10 @@
           <t>94967.99975956627</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>1779744</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>1779744.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38283,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38467,11 @@
           <t>122.4</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>108.56</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>99.39</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>108.56</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>99.39</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38518,16 @@
           <t>1308471.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>1439590.2</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>1439590.2</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>2092631.7</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>775565.44</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>775565.4399999999</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38544,10 @@
           <t>96037.34999571112</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>1308471</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>1308471.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
@@ -39241,7 +38713,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -39425,15 +38897,11 @@
           <t>27.2</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>28.77</t>
-        </is>
-      </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>30.33</t>
-        </is>
+      <c r="AM90" t="n">
+        <v>28.77</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>30.33</v>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
@@ -39480,20 +38948,16 @@
           <t>90130496.0</t>
         </is>
       </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>102891471.6</t>
-        </is>
+      <c r="AX90" t="n">
+        <v>102891471.6</v>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
           <t>139976545.9</t>
         </is>
       </c>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>162929477.08</t>
-        </is>
+      <c r="AZ90" t="n">
+        <v>162929477.08</v>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
@@ -39510,8 +38974,10 @@
           <t>-8302235.025979221</t>
         </is>
       </c>
-      <c r="BD90" t="n">
-        <v>90130496</v>
+      <c r="BD90" t="inlineStr">
+        <is>
+          <t>90130496.0</t>
+        </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
@@ -39677,7 +39143,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -39861,15 +39327,11 @@
           <t>26.99</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>29.02</t>
-        </is>
-      </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>30.41</t>
-        </is>
+      <c r="AM91" t="n">
+        <v>29.02</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>30.41</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
@@ -39916,20 +39378,16 @@
           <t>116543934.0</t>
         </is>
       </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>110660624.8</t>
-        </is>
+      <c r="AX91" t="n">
+        <v>110660624.8</v>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
           <t>154792338.5</t>
         </is>
       </c>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>167930362.34</t>
-        </is>
+      <c r="AZ91" t="n">
+        <v>167930362.34</v>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
@@ -39946,8 +39404,10 @@
           <t>-6234570.233193085</t>
         </is>
       </c>
-      <c r="BD91" t="n">
-        <v>116543934</v>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>116543934.0</t>
+        </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
@@ -40113,7 +39573,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -40297,15 +39757,11 @@
           <t>26.85</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>29.29</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>30.48</t>
-        </is>
+      <c r="AM92" t="n">
+        <v>29.29</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>30.48</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
@@ -40352,20 +39808,16 @@
           <t>105477076.0</t>
         </is>
       </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>123333532.4</t>
-        </is>
+      <c r="AX92" t="n">
+        <v>123333532.4</v>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
           <t>155136214.6</t>
         </is>
       </c>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>169872793.4</t>
-        </is>
+      <c r="AZ92" t="n">
+        <v>169872793.4</v>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
@@ -40382,8 +39834,10 @@
           <t>-5888111.378027424</t>
         </is>
       </c>
-      <c r="BD92" t="n">
-        <v>105477076</v>
+      <c r="BD92" t="inlineStr">
+        <is>
+          <t>105477076.0</t>
+        </is>
       </c>
       <c r="BE92" t="inlineStr">
         <is>
@@ -40549,7 +40003,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -40733,15 +40187,11 @@
           <t>27.0</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>29.58</t>
-        </is>
-      </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>30.55</t>
-        </is>
+      <c r="AM93" t="n">
+        <v>29.58</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>30.55</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
@@ -40788,20 +40238,16 @@
           <t>106737599.0</t>
         </is>
       </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>132241859.8</t>
-        </is>
+      <c r="AX93" t="n">
+        <v>132241859.8</v>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
           <t>153400791.7</t>
         </is>
       </c>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>175800706.34</t>
-        </is>
+      <c r="AZ93" t="n">
+        <v>175800706.34</v>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
@@ -40818,8 +40264,10 @@
           <t>-3997145.678575486</t>
         </is>
       </c>
-      <c r="BD93" t="n">
-        <v>106737599</v>
+      <c r="BD93" t="inlineStr">
+        <is>
+          <t>106737599.0</t>
+        </is>
       </c>
       <c r="BE93" t="inlineStr">
         <is>
@@ -40985,7 +40433,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -41169,15 +40617,11 @@
           <t>27.16</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>29.84</t>
-        </is>
-      </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>30.65</t>
-        </is>
+      <c r="AM94" t="n">
+        <v>29.84</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>30.65</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
@@ -41224,20 +40668,16 @@
           <t>95568253.0</t>
         </is>
       </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>148004191.6</t>
-        </is>
+      <c r="AX94" t="n">
+        <v>148004191.6</v>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
           <t>154119988.6</t>
         </is>
       </c>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>183315477.76</t>
-        </is>
+      <c r="AZ94" t="n">
+        <v>183315477.76</v>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
@@ -41254,8 +40694,10 @@
           <t>-1288066.94083789</t>
         </is>
       </c>
-      <c r="BD94" t="n">
-        <v>95568253</v>
+      <c r="BD94" t="inlineStr">
+        <is>
+          <t>95568253.0</t>
+        </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
@@ -41421,7 +40863,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -41605,15 +41047,11 @@
           <t>27.35</t>
         </is>
       </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>30.06</t>
-        </is>
-      </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>30.76</t>
-        </is>
+      <c r="AM95" t="n">
+        <v>30.06</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>30.76</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -41660,20 +41098,16 @@
           <t>128976262.0</t>
         </is>
       </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>177061620.2</t>
-        </is>
+      <c r="AX95" t="n">
+        <v>177061620.2</v>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
           <t>155197777.5</t>
         </is>
       </c>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>212132753.64</t>
-        </is>
+      <c r="AZ95" t="n">
+        <v>212132753.64</v>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
@@ -41690,8 +41124,10 @@
           <t>3824763.575245768</t>
         </is>
       </c>
-      <c r="BD95" t="n">
-        <v>128976262</v>
+      <c r="BD95" t="inlineStr">
+        <is>
+          <t>128976262.0</t>
+        </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
@@ -41857,7 +41293,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -42041,15 +41477,11 @@
           <t>27.75</t>
         </is>
       </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>30.28</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>30.85</t>
-        </is>
+      <c r="AM96" t="n">
+        <v>30.28</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>30.85</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -42096,20 +41528,16 @@
           <t>179908472.0</t>
         </is>
       </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>198924052.2</t>
-        </is>
+      <c r="AX96" t="n">
+        <v>198924052.2</v>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
           <t>151303002.4</t>
         </is>
       </c>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>221958679.64</t>
-        </is>
+      <c r="AZ96" t="n">
+        <v>221958679.64</v>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
@@ -42126,8 +41554,10 @@
           <t>7412778.934820741</t>
         </is>
       </c>
-      <c r="BD96" t="n">
-        <v>179908472</v>
+      <c r="BD96" t="inlineStr">
+        <is>
+          <t>179908472.0</t>
+        </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
@@ -42293,7 +41723,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -42477,15 +41907,11 @@
           <t>28.34</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>30.51</t>
-        </is>
-      </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>30.94</t>
-        </is>
+      <c r="AM97" t="n">
+        <v>30.51</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>30.94</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
@@ -42532,20 +41958,16 @@
           <t>150018713.0</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>186938896.8</t>
-        </is>
+      <c r="AX97" t="n">
+        <v>186938896.8</v>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
           <t>144140116.0</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>249744552.38</t>
-        </is>
+      <c r="AZ97" t="n">
+        <v>249744552.38</v>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
@@ -42562,8 +41984,10 @@
           <t>6816750.557969987</t>
         </is>
       </c>
-      <c r="BD97" t="n">
-        <v>150018713</v>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>150018713.0</t>
+        </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
@@ -42729,7 +42153,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -42913,15 +42337,11 @@
           <t>28.82</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>30.68</t>
-        </is>
-      </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>31.06</t>
-        </is>
+      <c r="AM98" t="n">
+        <v>30.68</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>31.06</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -42968,20 +42388,16 @@
           <t>185549258.0</t>
         </is>
       </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>174559723.6</t>
-        </is>
+      <c r="AX98" t="n">
+        <v>174559723.6</v>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
           <t>137660190.9</t>
         </is>
       </c>
-      <c r="AZ98" t="inlineStr">
-        <is>
-          <t>308682445.76</t>
-        </is>
+      <c r="AZ98" t="n">
+        <v>308682445.76</v>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
@@ -42998,8 +42414,10 @@
           <t>8924300.249684244</t>
         </is>
       </c>
-      <c r="BD98" t="n">
-        <v>185549258</v>
+      <c r="BD98" t="inlineStr">
+        <is>
+          <t>185549258.0</t>
+        </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
@@ -43165,7 +42583,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -43349,15 +42767,11 @@
           <t>29.27</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>30.85</t>
-        </is>
-      </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>31.11</t>
-        </is>
+      <c r="AM99" t="n">
+        <v>30.85</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>31.11</v>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
@@ -43404,20 +42818,16 @@
           <t>240855396.0</t>
         </is>
       </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>160235785.6</t>
-        </is>
+      <c r="AX99" t="n">
+        <v>160235785.6</v>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
           <t>132464211.4</t>
         </is>
       </c>
-      <c r="AZ99" t="inlineStr">
-        <is>
-          <t>323808057.5</t>
-        </is>
+      <c r="AZ99" t="n">
+        <v>323808057.5</v>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
@@ -43434,8 +42844,10 @@
           <t>7809516.407501608</t>
         </is>
       </c>
-      <c r="BD99" t="n">
-        <v>240855396</v>
+      <c r="BD99" t="inlineStr">
+        <is>
+          <t>240855396.0</t>
+        </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
@@ -43601,7 +43013,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -43785,15 +43197,11 @@
           <t>29.7</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>30.98</t>
-        </is>
-      </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>31.1</t>
-        </is>
+      <c r="AM100" t="n">
+        <v>30.98</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>31.1</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -43840,20 +43248,16 @@
           <t>238288422.0</t>
         </is>
       </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>133333934.8</t>
-        </is>
+      <c r="AX100" t="n">
+        <v>133333934.8</v>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
           <t>124708175.2</t>
         </is>
       </c>
-      <c r="AZ100" t="inlineStr">
-        <is>
-          <t>321307698.24</t>
-        </is>
+      <c r="AZ100" t="n">
+        <v>321307698.24</v>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
@@ -43870,8 +43274,10 @@
           <t>12399.11840137839</t>
         </is>
       </c>
-      <c r="BD100" t="n">
-        <v>238288422</v>
+      <c r="BD100" t="inlineStr">
+        <is>
+          <t>238288422.0</t>
+        </is>
       </c>
       <c r="BE100" t="inlineStr">
         <is>
@@ -44037,7 +43443,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -44221,15 +43627,11 @@
           <t>22.26</t>
         </is>
       </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>21.94</t>
-        </is>
-      </c>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>16.94</t>
-        </is>
+      <c r="AM101" t="n">
+        <v>21.94</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>16.94</v>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
@@ -44276,20 +43678,16 @@
           <t>5884981.0</t>
         </is>
       </c>
-      <c r="AX101" t="inlineStr">
-        <is>
-          <t>4042712.8</t>
-        </is>
+      <c r="AX101" t="n">
+        <v>4042712.8</v>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
           <t>5488084.7</t>
         </is>
       </c>
-      <c r="AZ101" t="inlineStr">
-        <is>
-          <t>7917586.44</t>
-        </is>
+      <c r="AZ101" t="n">
+        <v>7917586.44</v>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
@@ -44306,8 +43704,10 @@
           <t>-720407.9029942201</t>
         </is>
       </c>
-      <c r="BD101" t="n">
-        <v>5884981</v>
+      <c r="BD101" t="inlineStr">
+        <is>
+          <t>5884981.0</t>
+        </is>
       </c>
       <c r="BE101" t="inlineStr">
         <is>
@@ -44473,7 +43873,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -44657,15 +44057,11 @@
           <t>21.98</t>
         </is>
       </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>21.96</t>
-        </is>
-      </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>16.69</t>
-        </is>
+      <c r="AM102" t="n">
+        <v>21.96</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>16.69</v>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
@@ -44712,20 +44108,16 @@
           <t>4421696.0</t>
         </is>
       </c>
-      <c r="AX102" t="inlineStr">
-        <is>
-          <t>3534974.8</t>
-        </is>
+      <c r="AX102" t="n">
+        <v>3534974.8</v>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
           <t>8331026.5</t>
         </is>
       </c>
-      <c r="AZ102" t="inlineStr">
-        <is>
-          <t>8489841.82</t>
-        </is>
+      <c r="AZ102" t="n">
+        <v>8489841.82</v>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
@@ -44742,8 +44134,10 @@
           <t>-869138.1947405227</t>
         </is>
       </c>
-      <c r="BD102" t="n">
-        <v>4421696</v>
+      <c r="BD102" t="inlineStr">
+        <is>
+          <t>4421696.0</t>
+        </is>
       </c>
       <c r="BE102" t="inlineStr">
         <is>
@@ -44909,7 +44303,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -45093,15 +44487,11 @@
           <t>21.6</t>
         </is>
       </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>21.96</t>
-        </is>
-      </c>
-      <c r="AN103" t="inlineStr">
-        <is>
-          <t>16.44</t>
-        </is>
+      <c r="AM103" t="n">
+        <v>21.96</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>16.44</v>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
@@ -45148,20 +44538,16 @@
           <t>3218966.0</t>
         </is>
       </c>
-      <c r="AX103" t="inlineStr">
-        <is>
-          <t>3493839.2</t>
-        </is>
+      <c r="AX103" t="n">
+        <v>3493839.2</v>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
           <t>8558865.6</t>
         </is>
       </c>
-      <c r="AZ103" t="inlineStr">
-        <is>
-          <t>8863790.8</t>
-        </is>
+      <c r="AZ103" t="n">
+        <v>8863790.800000001</v>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
@@ -45178,8 +44564,10 @@
           <t>-893788.8545659361</t>
         </is>
       </c>
-      <c r="BD103" t="n">
-        <v>3218966</v>
+      <c r="BD103" t="inlineStr">
+        <is>
+          <t>3218966.0</t>
+        </is>
       </c>
       <c r="BE103" t="inlineStr">
         <is>
@@ -45345,7 +44733,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -45529,15 +44917,11 @@
           <t>21.83</t>
         </is>
       </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>22.06</t>
-        </is>
-      </c>
-      <c r="AN104" t="inlineStr">
-        <is>
-          <t>16.21</t>
-        </is>
+      <c r="AM104" t="n">
+        <v>22.06</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>16.21</v>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
@@ -45584,20 +44968,16 @@
           <t>3250027.0</t>
         </is>
       </c>
-      <c r="AX104" t="inlineStr">
-        <is>
-          <t>4156867.8</t>
-        </is>
+      <c r="AX104" t="n">
+        <v>4156867.8</v>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
           <t>8635009.9</t>
         </is>
       </c>
-      <c r="AZ104" t="inlineStr">
-        <is>
-          <t>9165543.34</t>
-        </is>
+      <c r="AZ104" t="n">
+        <v>9165543.34</v>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
@@ -45614,8 +44994,10 @@
           <t>-768219.123796314</t>
         </is>
       </c>
-      <c r="BD104" t="n">
-        <v>3250027</v>
+      <c r="BD104" t="inlineStr">
+        <is>
+          <t>3250027.0</t>
+        </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
@@ -45781,7 +45163,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -45965,15 +45347,11 @@
           <t>22.36</t>
         </is>
       </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>22.2</t>
-        </is>
-      </c>
-      <c r="AN105" t="inlineStr">
-        <is>
-          <t>15.96</t>
-        </is>
+      <c r="AM105" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>15.96</v>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
@@ -46020,20 +45398,16 @@
           <t>3437894.0</t>
         </is>
       </c>
-      <c r="AX105" t="inlineStr">
-        <is>
-          <t>4851245.6</t>
-        </is>
+      <c r="AX105" t="n">
+        <v>4851245.6</v>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
           <t>8761358.7</t>
         </is>
       </c>
-      <c r="AZ105" t="inlineStr">
-        <is>
-          <t>9221054.22</t>
-        </is>
+      <c r="AZ105" t="n">
+        <v>9221054.220000001</v>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
@@ -46050,8 +45424,10 @@
           <t>-564725.3611327009</t>
         </is>
       </c>
-      <c r="BD105" t="n">
-        <v>3437894</v>
+      <c r="BD105" t="inlineStr">
+        <is>
+          <t>3437894.0</t>
+        </is>
       </c>
       <c r="BE105" t="inlineStr">
         <is>
@@ -46217,7 +45593,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -46401,15 +45777,11 @@
           <t>23.0</t>
         </is>
       </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>22.3</t>
-        </is>
-      </c>
-      <c r="AN106" t="inlineStr">
-        <is>
-          <t>15.69</t>
-        </is>
+      <c r="AM106" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>15.69</v>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
@@ -46456,20 +45828,16 @@
           <t>3346291.0</t>
         </is>
       </c>
-      <c r="AX106" t="inlineStr">
-        <is>
-          <t>6933456.6</t>
-        </is>
+      <c r="AX106" t="n">
+        <v>6933456.6</v>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
           <t>8914002.2</t>
         </is>
       </c>
-      <c r="AZ106" t="inlineStr">
-        <is>
-          <t>9240023.96</t>
-        </is>
+      <c r="AZ106" t="n">
+        <v>9240023.960000001</v>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
@@ -46486,8 +45854,10 @@
           <t>-273979.8301442275</t>
         </is>
       </c>
-      <c r="BD106" t="n">
-        <v>3346291</v>
+      <c r="BD106" t="inlineStr">
+        <is>
+          <t>3346291.0</t>
+        </is>
       </c>
       <c r="BE106" t="inlineStr">
         <is>
@@ -46653,7 +46023,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -46837,15 +46207,11 @@
           <t>23.71</t>
         </is>
       </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>22.42</t>
-        </is>
-      </c>
-      <c r="AN107" t="inlineStr">
-        <is>
-          <t>15.42</t>
-        </is>
+      <c r="AM107" t="n">
+        <v>22.42</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>15.42</v>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
@@ -46892,20 +46258,16 @@
           <t>4216018.0</t>
         </is>
       </c>
-      <c r="AX107" t="inlineStr">
-        <is>
-          <t>13127078.2</t>
-        </is>
+      <c r="AX107" t="n">
+        <v>13127078.2</v>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
           <t>9389102.3</t>
         </is>
       </c>
-      <c r="AZ107" t="inlineStr">
-        <is>
-          <t>9278927.06</t>
-        </is>
+      <c r="AZ107" t="n">
+        <v>9278927.060000001</v>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
@@ -46922,8 +46284,10 @@
           <t>160970.5294873137</t>
         </is>
       </c>
-      <c r="BD107" t="n">
-        <v>4216018</v>
+      <c r="BD107" t="inlineStr">
+        <is>
+          <t>4216018.0</t>
+        </is>
       </c>
       <c r="BE107" t="inlineStr">
         <is>
@@ -47089,7 +46453,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -47273,15 +46637,11 @@
           <t>24.32</t>
         </is>
       </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>22.5</t>
-        </is>
-      </c>
-      <c r="AN108" t="inlineStr">
-        <is>
-          <t>15.16</t>
-        </is>
+      <c r="AM108" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>15.16</v>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
@@ -47328,20 +46688,16 @@
           <t>6534109.0</t>
         </is>
       </c>
-      <c r="AX108" t="inlineStr">
-        <is>
-          <t>13623892.0</t>
-        </is>
+      <c r="AX108" t="n">
+        <v>13623892</v>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
           <t>9462521.1</t>
         </is>
       </c>
-      <c r="AZ108" t="inlineStr">
-        <is>
-          <t>9280602.78</t>
-        </is>
+      <c r="AZ108" t="n">
+        <v>9280602.779999999</v>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
@@ -47358,8 +46714,10 @@
           <t>683394.2029078249</t>
         </is>
       </c>
-      <c r="BD108" t="n">
-        <v>6534109</v>
+      <c r="BD108" t="inlineStr">
+        <is>
+          <t>6534109.0</t>
+        </is>
       </c>
       <c r="BE108" t="inlineStr">
         <is>
@@ -47525,7 +46883,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -47709,15 +47067,11 @@
           <t>24.3</t>
         </is>
       </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>21.89</t>
-        </is>
-      </c>
-      <c r="AN109" t="inlineStr">
-        <is>
-          <t>14.88</t>
-        </is>
+      <c r="AM109" t="n">
+        <v>21.89</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>14.88</v>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
@@ -47764,20 +47118,16 @@
           <t>6721916.0</t>
         </is>
       </c>
-      <c r="AX109" t="inlineStr">
-        <is>
-          <t>13113152.0</t>
-        </is>
+      <c r="AX109" t="n">
+        <v>13113152</v>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
           <t>9484719.5</t>
         </is>
       </c>
-      <c r="AZ109" t="inlineStr">
-        <is>
-          <t>9206563.84</t>
-        </is>
+      <c r="AZ109" t="n">
+        <v>9206563.84</v>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
@@ -47794,8 +47144,10 @@
           <t>1156939.907690417</t>
         </is>
       </c>
-      <c r="BD109" t="n">
-        <v>6721916</v>
+      <c r="BD109" t="inlineStr">
+        <is>
+          <t>6721916.0</t>
+        </is>
       </c>
       <c r="BE109" t="inlineStr">
         <is>
@@ -47961,7 +47313,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -48145,15 +47497,11 @@
           <t>23.58</t>
         </is>
       </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>21.19</t>
-        </is>
-      </c>
-      <c r="AN110" t="inlineStr">
-        <is>
-          <t>14.57</t>
-        </is>
+      <c r="AM110" t="n">
+        <v>21.19</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>14.57</v>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
@@ -48200,20 +47548,16 @@
           <t>13848949.0</t>
         </is>
       </c>
-      <c r="AX110" t="inlineStr">
-        <is>
-          <t>12671471.8</t>
-        </is>
+      <c r="AX110" t="n">
+        <v>12671471.8</v>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
           <t>9650224.6</t>
         </is>
       </c>
-      <c r="AZ110" t="inlineStr">
-        <is>
-          <t>9151505.9</t>
-        </is>
+      <c r="AZ110" t="n">
+        <v>9151505.9</v>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
@@ -48230,8 +47574,10 @@
           <t>1771992.310676605</t>
         </is>
       </c>
-      <c r="BD110" t="n">
-        <v>13848949</v>
+      <c r="BD110" t="inlineStr">
+        <is>
+          <t>13848949.0</t>
+        </is>
       </c>
       <c r="BE110" t="inlineStr">
         <is>
@@ -48397,7 +47743,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -48581,15 +47927,11 @@
           <t>22.18</t>
         </is>
       </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>20.39</t>
-        </is>
-      </c>
-      <c r="AN111" t="inlineStr">
-        <is>
-          <t>14.23</t>
-        </is>
+      <c r="AM111" t="n">
+        <v>20.39</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>14.23</v>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
@@ -48636,20 +47978,16 @@
           <t>34314399.0</t>
         </is>
       </c>
-      <c r="AX111" t="inlineStr">
-        <is>
-          <t>10894547.8</t>
-        </is>
+      <c r="AX111" t="n">
+        <v>10894547.8</v>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
           <t>8866956.3</t>
         </is>
       </c>
-      <c r="AZ111" t="inlineStr">
-        <is>
-          <t>8922795.38</t>
-        </is>
+      <c r="AZ111" t="n">
+        <v>8922795.380000001</v>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
@@ -48666,8 +48004,10 @@
           <t>1823742.482418425</t>
         </is>
       </c>
-      <c r="BD111" t="n">
-        <v>34314399</v>
+      <c r="BD111" t="inlineStr">
+        <is>
+          <t>34314399.0</t>
+        </is>
       </c>
       <c r="BE111" t="inlineStr">
         <is>
@@ -48833,7 +48173,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -49017,15 +48357,11 @@
           <t>919.4</t>
         </is>
       </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>948.95</t>
-        </is>
-      </c>
-      <c r="AN112" t="inlineStr">
-        <is>
-          <t>947.82</t>
-        </is>
+      <c r="AM112" t="n">
+        <v>948.95</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>947.8200000000001</v>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
@@ -49072,20 +48408,16 @@
           <t>10702402903.0</t>
         </is>
       </c>
-      <c r="AX112" t="inlineStr">
-        <is>
-          <t>13777681330.2</t>
-        </is>
+      <c r="AX112" t="n">
+        <v>13777681330.2</v>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
           <t>13184190874.5</t>
         </is>
       </c>
-      <c r="AZ112" t="inlineStr">
-        <is>
-          <t>14165986897.28</t>
-        </is>
+      <c r="AZ112" t="n">
+        <v>14165986897.28</v>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
@@ -49102,8 +48434,10 @@
           <t>-288049536.2624874</t>
         </is>
       </c>
-      <c r="BD112" t="n">
-        <v>10702402903</v>
+      <c r="BD112" t="inlineStr">
+        <is>
+          <t>10702402903.0</t>
+        </is>
       </c>
       <c r="BE112" t="inlineStr">
         <is>
@@ -49269,7 +48603,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -49453,15 +48787,11 @@
           <t>909.2</t>
         </is>
       </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>954.7</t>
-        </is>
-      </c>
-      <c r="AN113" t="inlineStr">
-        <is>
-          <t>945.54</t>
-        </is>
+      <c r="AM113" t="n">
+        <v>954.7</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>945.54</v>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
@@ -49508,20 +48838,16 @@
           <t>9579043601.0</t>
         </is>
       </c>
-      <c r="AX113" t="inlineStr">
-        <is>
-          <t>13831910429.6</t>
-        </is>
+      <c r="AX113" t="n">
+        <v>13831910429.6</v>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
           <t>13509805904.0</t>
         </is>
       </c>
-      <c r="AZ113" t="inlineStr">
-        <is>
-          <t>14413977761.06</t>
-        </is>
+      <c r="AZ113" t="n">
+        <v>14413977761.06</v>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
@@ -49538,8 +48864,10 @@
           <t>-94238805.57345963</t>
         </is>
       </c>
-      <c r="BD113" t="n">
-        <v>9579043601</v>
+      <c r="BD113" t="inlineStr">
+        <is>
+          <t>9579043601.0</t>
+        </is>
       </c>
       <c r="BE113" t="inlineStr">
         <is>
@@ -49705,7 +49033,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -49889,15 +49217,11 @@
           <t>906.8</t>
         </is>
       </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>962.95</t>
-        </is>
-      </c>
-      <c r="AN114" t="inlineStr">
-        <is>
-          <t>944.08</t>
-        </is>
+      <c r="AM114" t="n">
+        <v>962.95</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>944.08</v>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
@@ -49944,20 +49268,16 @@
           <t>16911194399.0</t>
         </is>
       </c>
-      <c r="AX114" t="inlineStr">
-        <is>
-          <t>14386844246.4</t>
-        </is>
+      <c r="AX114" t="n">
+        <v>14386844246.4</v>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
           <t>13675683609.2</t>
         </is>
       </c>
-      <c r="AZ114" t="inlineStr">
-        <is>
-          <t>14618581897.64</t>
-        </is>
+      <c r="AZ114" t="n">
+        <v>14618581897.64</v>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
@@ -49974,8 +49294,10 @@
           <t>306359263.681345</t>
         </is>
       </c>
-      <c r="BD114" t="n">
-        <v>16911194399</v>
+      <c r="BD114" t="inlineStr">
+        <is>
+          <t>16911194399.0</t>
+        </is>
       </c>
       <c r="BE114" t="inlineStr">
         <is>
@@ -50141,7 +49463,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -50325,15 +49647,11 @@
           <t>911.4</t>
         </is>
       </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>971.8</t>
-        </is>
-      </c>
-      <c r="AN115" t="inlineStr">
-        <is>
-          <t>941.9</t>
-        </is>
+      <c r="AM115" t="n">
+        <v>971.8</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>941.9</v>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
@@ -50380,20 +49698,16 @@
           <t>15812987742.0</t>
         </is>
       </c>
-      <c r="AX115" t="inlineStr">
-        <is>
-          <t>13146559354.4</t>
-        </is>
+      <c r="AX115" t="n">
+        <v>13146559354.4</v>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
           <t>13118876980.5</t>
         </is>
       </c>
-      <c r="AZ115" t="inlineStr">
-        <is>
-          <t>14614553602.28</t>
-        </is>
+      <c r="AZ115" t="n">
+        <v>14614553602.28</v>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
@@ -50410,8 +49724,10 @@
           <t>82113231.98530579</t>
         </is>
       </c>
-      <c r="BD115" t="n">
-        <v>15812987742</v>
+      <c r="BD115" t="inlineStr">
+        <is>
+          <t>15812987742.0</t>
+        </is>
       </c>
       <c r="BE115" t="inlineStr">
         <is>
@@ -50577,7 +49893,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -50761,15 +50077,11 @@
           <t>916.8</t>
         </is>
       </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>977.55</t>
-        </is>
-      </c>
-      <c r="AN116" t="inlineStr">
-        <is>
-          <t>938.52</t>
-        </is>
+      <c r="AM116" t="n">
+        <v>977.55</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>938.52</v>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
@@ -50816,20 +50128,16 @@
           <t>15882778006.0</t>
         </is>
       </c>
-      <c r="AX116" t="inlineStr">
-        <is>
-          <t>13620510362.4</t>
-        </is>
+      <c r="AX116" t="n">
+        <v>13620510362.4</v>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
           <t>12470961715.4</t>
         </is>
       </c>
-      <c r="AZ116" t="inlineStr">
-        <is>
-          <t>14466055493.78</t>
-        </is>
+      <c r="AZ116" t="n">
+        <v>14466055493.78</v>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
@@ -50846,8 +50154,10 @@
           <t>-123505858.3299389</t>
         </is>
       </c>
-      <c r="BD116" t="n">
-        <v>15882778006</v>
+      <c r="BD116" t="inlineStr">
+        <is>
+          <t>15882778006.0</t>
+        </is>
       </c>
       <c r="BE116" t="inlineStr">
         <is>
@@ -51013,7 +50323,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -51197,15 +50507,11 @@
           <t>917.6</t>
         </is>
       </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>980.85</t>
-        </is>
-      </c>
-      <c r="AN117" t="inlineStr">
-        <is>
-          <t>933.96</t>
-        </is>
+      <c r="AM117" t="n">
+        <v>980.85</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>933.96</v>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
@@ -51252,20 +50558,16 @@
           <t>10973548400.0</t>
         </is>
       </c>
-      <c r="AX117" t="inlineStr">
-        <is>
-          <t>12590700418.8</t>
-        </is>
+      <c r="AX117" t="n">
+        <v>12590700418.8</v>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
           <t>11918833012.0</t>
         </is>
       </c>
-      <c r="AZ117" t="inlineStr">
-        <is>
-          <t>14368721493.28</t>
-        </is>
+      <c r="AZ117" t="n">
+        <v>14368721493.28</v>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
@@ -51282,8 +50584,10 @@
           <t>-420314020.6970749</t>
         </is>
       </c>
-      <c r="BD117" t="n">
-        <v>10973548400</v>
+      <c r="BD117" t="inlineStr">
+        <is>
+          <t>10973548400.0</t>
+        </is>
       </c>
       <c r="BE117" t="inlineStr">
         <is>
@@ -51449,7 +50753,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -51633,15 +50937,11 @@
           <t>932.2</t>
         </is>
       </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>987.15</t>
-        </is>
-      </c>
-      <c r="AN118" t="inlineStr">
-        <is>
-          <t>929.9</t>
-        </is>
+      <c r="AM118" t="n">
+        <v>987.15</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>929.9</v>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
@@ -51688,20 +50988,16 @@
           <t>12353712685.0</t>
         </is>
       </c>
-      <c r="AX118" t="inlineStr">
-        <is>
-          <t>13187701378.4</t>
-        </is>
+      <c r="AX118" t="n">
+        <v>13187701378.4</v>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
           <t>12539817288.3</t>
         </is>
       </c>
-      <c r="AZ118" t="inlineStr">
-        <is>
-          <t>14292572173.18</t>
-        </is>
+      <c r="AZ118" t="n">
+        <v>14292572173.18</v>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
@@ -51718,8 +51014,10 @@
           <t>-303325579.8395176</t>
         </is>
       </c>
-      <c r="BD118" t="n">
-        <v>12353712685</v>
+      <c r="BD118" t="inlineStr">
+        <is>
+          <t>12353712685.0</t>
+        </is>
       </c>
       <c r="BE118" t="inlineStr">
         <is>
@@ -51885,7 +51183,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -52069,15 +51367,11 @@
           <t>947.0</t>
         </is>
       </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>993.0</t>
-        </is>
-      </c>
-      <c r="AN119" t="inlineStr">
-        <is>
-          <t>925.54</t>
-        </is>
+      <c r="AM119" t="n">
+        <v>993</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>925.54</v>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
@@ -52124,20 +51418,16 @@
           <t>10709769939.0</t>
         </is>
       </c>
-      <c r="AX119" t="inlineStr">
-        <is>
-          <t>12964522972.0</t>
-        </is>
+      <c r="AX119" t="n">
+        <v>12964522972</v>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
           <t>13184192924.4</t>
         </is>
       </c>
-      <c r="AZ119" t="inlineStr">
-        <is>
-          <t>14209168625.62</t>
-        </is>
+      <c r="AZ119" t="n">
+        <v>14209168625.62</v>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
@@ -52154,8 +51444,10 @@
           <t>-273240924.15588</t>
         </is>
       </c>
-      <c r="BD119" t="n">
-        <v>10709769939</v>
+      <c r="BD119" t="inlineStr">
+        <is>
+          <t>10709769939.0</t>
+        </is>
       </c>
       <c r="BE119" t="inlineStr">
         <is>
@@ -52321,7 +51613,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -52505,15 +51797,11 @@
           <t>960.2</t>
         </is>
       </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>997.15</t>
-        </is>
-      </c>
-      <c r="AN120" t="inlineStr">
-        <is>
-          <t>920.92</t>
-        </is>
+      <c r="AM120" t="n">
+        <v>997.15</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>920.92</v>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
@@ -52560,20 +51848,16 @@
           <t>18182742782.0</t>
         </is>
       </c>
-      <c r="AX120" t="inlineStr">
-        <is>
-          <t>13091194606.6</t>
-        </is>
+      <c r="AX120" t="n">
+        <v>13091194606.6</v>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
           <t>13748861147.6</t>
         </is>
       </c>
-      <c r="AZ120" t="inlineStr">
-        <is>
-          <t>14155319682.02</t>
-        </is>
+      <c r="AZ120" t="n">
+        <v>14155319682.02</v>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
@@ -52590,8 +51874,10 @@
           <t>-44367517.38797188</t>
         </is>
       </c>
-      <c r="BD120" t="n">
-        <v>18182742782</v>
+      <c r="BD120" t="inlineStr">
+        <is>
+          <t>18182742782.0</t>
+        </is>
       </c>
       <c r="BE120" t="inlineStr">
         <is>
@@ -52757,7 +52043,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -52941,15 +52227,11 @@
           <t>968.8</t>
         </is>
       </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>1002.3</t>
-        </is>
-      </c>
-      <c r="AN121" t="inlineStr">
-        <is>
-          <t>916.24</t>
-        </is>
+      <c r="AM121" t="n">
+        <v>1002.3</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>916.24</v>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
@@ -52996,20 +52278,16 @@
           <t>10733728288.0</t>
         </is>
       </c>
-      <c r="AX121" t="inlineStr">
-        <is>
-          <t>11321413068.4</t>
-        </is>
+      <c r="AX121" t="n">
+        <v>11321413068.4</v>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
           <t>14033372540.0</t>
         </is>
       </c>
-      <c r="AZ121" t="inlineStr">
-        <is>
-          <t>13994353884.38</t>
-        </is>
+      <c r="AZ121" t="n">
+        <v>13994353884.38</v>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
@@ -53026,8 +52304,10 @@
           <t>-516496615.2771072</t>
         </is>
       </c>
-      <c r="BD121" t="n">
-        <v>10733728288</v>
+      <c r="BD121" t="inlineStr">
+        <is>
+          <t>10733728288.0</t>
+        </is>
       </c>
       <c r="BE121" t="inlineStr">
         <is>
@@ -53193,7 +52473,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -53377,15 +52657,11 @@
           <t>972.8</t>
         </is>
       </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>1005.15</t>
-        </is>
-      </c>
-      <c r="AN122" t="inlineStr">
-        <is>
-          <t>911.3</t>
-        </is>
+      <c r="AM122" t="n">
+        <v>1005.15</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>911.3</v>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
@@ -53432,20 +52708,16 @@
           <t>13958553198.0</t>
         </is>
       </c>
-      <c r="AX122" t="inlineStr">
-        <is>
-          <t>11246965605.2</t>
-        </is>
+      <c r="AX122" t="n">
+        <v>11246965605.2</v>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
           <t>15377407355.7</t>
         </is>
       </c>
-      <c r="AZ122" t="inlineStr">
-        <is>
-          <t>13940555876.02</t>
-        </is>
+      <c r="AZ122" t="n">
+        <v>13940555876.02</v>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
@@ -53462,8 +52734,10 @@
           <t>-374411751.6445465</t>
         </is>
       </c>
-      <c r="BD122" t="n">
-        <v>13958553198</v>
+      <c r="BD122" t="inlineStr">
+        <is>
+          <t>13958553198.0</t>
+        </is>
       </c>
       <c r="BE122" t="inlineStr">
         <is>
